--- a/events/LiptovskyMikulas_2018_WC/LiptovskyMikulas_2018_WC_start.xlsx
+++ b/events/LiptovskyMikulas_2018_WC/LiptovskyMikulas_2018_WC_start.xlsx
@@ -1467,11 +1467,6 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>84121</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41015,11 +41010,6 @@
       <c r="R686" t="inlineStr">
         <is>
           <t>STANOVSKY Samuel</t>
-        </is>
-      </c>
-      <c r="U686" t="inlineStr">
-        <is>
-          <t>84121</t>
         </is>
       </c>
     </row>

--- a/events/LiptovskyMikulas_2018_WC/LiptovskyMikulas_2018_WC_start.xlsx
+++ b/events/LiptovskyMikulas_2018_WC/LiptovskyMikulas_2018_WC_start.xlsx
@@ -33236,6 +33236,11 @@
           <t>JANE Jakub</t>
         </is>
       </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
       <c r="Y559" t="inlineStr">
         <is>
           <t>35061</t>
@@ -33994,6 +33999,11 @@
       <c r="S569" t="inlineStr">
         <is>
           <t>JANE Jakub</t>
+        </is>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
       <c r="Y569" t="inlineStr">
